--- a/DCF resources/CFI_DCF-Model.xlsx
+++ b/DCF resources/CFI_DCF-Model.xlsx
@@ -744,6 +744,54 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>714374</colOff>
+      <row>3</row>
+      <rowOff>19050</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>655477</colOff>
+      <row>9</row>
+      <rowOff>114300</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1">
+          <a:hlinkClick r:id="rId1"/>
+        </cNvPr>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="1447799" y="762000"/>
+          <a:ext cx="3359943" cy="1581150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
@@ -770,6 +818,49 @@
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>13</col>
+      <colOff>107951</colOff>
+      <row>42</row>
+      <rowOff>129314</rowOff>
+    </from>
+    <to>
+      <col>13</col>
+      <colOff>848361</colOff>
+      <row>46</row>
+      <rowOff>104773</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1">
+          <a:hlinkClick r:id="rId1"/>
+        </cNvPr>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="10439401" y="8714514"/>
+          <a:ext cx="742950" cy="788259"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
     <clientData/>
   </twoCellAnchor>
 </wsDr>
@@ -1205,7 +1296,7 @@
       <c r="B12" s="50" t="n"/>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>FICO — DCF Model (CFI template, populated)</t>
+          <t>FICO — DCF Model</t>
         </is>
       </c>
       <c r="D12" s="50" t="n"/>
@@ -1353,7 +1444,7 @@
       <c r="B20" s="50" t="n"/>
       <c r="C20" s="56" t="inlineStr">
         <is>
-          <t>Populated with Fair Isaac Corp (FICO) SEC fundamentals and base-case projections. Educational use only.</t>
+          <t>Populated with Fair Isaac Corp (FICO) projections from SEC fundamentals. Units: $ thousands.</t>
         </is>
       </c>
       <c r="D20" s="56" t="n"/>
@@ -1373,7 +1464,7 @@
       <c r="B21" s="50" t="n"/>
       <c r="C21" s="50" t="inlineStr">
         <is>
-          <t>Sources: FY2025 10-K, Q3 FY2026 10-Q, Yahoo Finance market data. Units: $ thousands except per-share price.</t>
+          <t>Yellow/blue = inputs. Educational only — not investment advice.</t>
         </is>
       </c>
       <c r="D21" s="50" t="n"/>
@@ -1559,6 +1650,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" scale="64"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2115,19 +2207,19 @@
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="73" t="n">
-        <v>1032663.8</v>
+        <v>1052473.5</v>
       </c>
       <c r="F21" s="73" t="n">
-        <v>1143873.7</v>
+        <v>1288114</v>
       </c>
       <c r="G21" s="73" t="n">
-        <v>1244280.4</v>
+        <v>1517363.4</v>
       </c>
       <c r="H21" s="73" t="n">
-        <v>1341026.7</v>
+        <v>1729936.7</v>
       </c>
       <c r="I21" s="73" t="n">
-        <v>1448308.8</v>
+        <v>1952571.6</v>
       </c>
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
@@ -2869,7 +2961,7 @@
       <c r="A51" s="23" t="n"/>
       <c r="B51" s="78" t="inlineStr">
         <is>
-          <t>EBIT path: FY25A margin 46.5% fading to 44% by FY29-30; revenue growth 14%→8%.</t>
+          <t>Debt/Cash from 10-Q 2026-06-30. Shares/price from market. Tax 18.8% FY25 ETR.</t>
         </is>
       </c>
       <c r="C51" s="23" t="n"/>
@@ -2885,7 +2977,7 @@
       <c r="A52" s="23" t="n"/>
       <c r="B52" s="78" t="inlineStr">
         <is>
-          <t>Debt/Cash from 10-Q ended 2026-06-30 (latest). Shares = diluted shares outstanding (Yahoo).</t>
+          <t>EBIT path uses same growth/COGS/opex logic as the FICO 3-statement forecast.</t>
         </is>
       </c>
       <c r="C52" s="23" t="n"/>
@@ -2904,11 +2996,7 @@
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="23" t="n"/>
-      <c r="B53" s="78" t="inlineStr">
-        <is>
-          <t>WACC ~9.6% (rf 4.3%, beta 1.32, ERP 5%, 80/20 E/D, pre-tax kd 5.5%). Units $000s.</t>
-        </is>
-      </c>
+      <c r="B53" s="23" t="n"/>
       <c r="C53" s="23" t="n"/>
       <c r="D53" s="10" t="n"/>
       <c r="E53" s="23" t="n"/>

--- a/DCF resources/CFI_DCF-Model.xlsx
+++ b/DCF resources/CFI_DCF-Model.xlsx
@@ -1296,7 +1296,7 @@
       <c r="B12" s="50" t="n"/>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>FICO — DCF Model</t>
+          <t>FICO — DCF Model (CFI template)</t>
         </is>
       </c>
       <c r="D12" s="50" t="n"/>
@@ -1444,7 +1444,7 @@
       <c r="B20" s="50" t="n"/>
       <c r="C20" s="56" t="inlineStr">
         <is>
-          <t>Populated with Fair Isaac Corp (FICO) projections from SEC fundamentals. Units: $ thousands.</t>
+          <t>DCF assumptions + forecast drivers from FICO SEC/market data. Formulas preserved.</t>
         </is>
       </c>
       <c r="D20" s="56" t="n"/>
@@ -1464,7 +1464,7 @@
       <c r="B21" s="50" t="n"/>
       <c r="C21" s="50" t="inlineStr">
         <is>
-          <t>Yellow/blue = inputs. Educational only — not investment advice.</t>
+          <t>All content is Copyright material of CFI Education Inc.</t>
         </is>
       </c>
       <c r="D21" s="50" t="n"/>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="68" t="n">
-        <v>0.188</v>
+        <v>0.1877</v>
       </c>
       <c r="E5" s="21" t="n"/>
       <c r="F5" s="23" t="n"/>
@@ -2207,19 +2207,19 @@
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="73" t="n">
-        <v>1052473.5</v>
+        <v>1048623.4</v>
       </c>
       <c r="F21" s="73" t="n">
-        <v>1288114</v>
+        <v>1284433.8</v>
       </c>
       <c r="G21" s="73" t="n">
-        <v>1517363.4</v>
+        <v>1505458.6</v>
       </c>
       <c r="H21" s="73" t="n">
-        <v>1729936.7</v>
+        <v>1717399.8</v>
       </c>
       <c r="I21" s="73" t="n">
-        <v>1952571.6</v>
+        <v>1922965.4</v>
       </c>
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
@@ -2946,7 +2946,7 @@
       <c r="A50" s="23" t="n"/>
       <c r="B50" s="78" t="inlineStr">
         <is>
-          <t>FICO notes</t>
+          <t>FICO DCF inputs from SEC + market bridge (10-Q debt/cash). Yellow/blue = inputs.</t>
         </is>
       </c>
       <c r="C50" s="23" t="n"/>
@@ -2959,11 +2959,7 @@
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="23" t="n"/>
-      <c r="B51" s="78" t="inlineStr">
-        <is>
-          <t>Debt/Cash from 10-Q 2026-06-30. Shares/price from market. Tax 18.8% FY25 ETR.</t>
-        </is>
-      </c>
+      <c r="B51" s="23" t="n"/>
       <c r="C51" s="23" t="n"/>
       <c r="D51" s="10" t="n"/>
       <c r="E51" s="23" t="n"/>
@@ -2975,11 +2971,7 @@
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="23" t="n"/>
-      <c r="B52" s="78" t="inlineStr">
-        <is>
-          <t>EBIT path uses same growth/COGS/opex logic as the FICO 3-statement forecast.</t>
-        </is>
-      </c>
+      <c r="B52" s="23" t="n"/>
       <c r="C52" s="23" t="n"/>
       <c r="D52" s="10" t="n"/>
       <c r="E52" s="23" t="n"/>
